--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20010" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_盖亚之心（中）" sheetId="1" r:id="rId1"/>
@@ -375,7 +375,33 @@
     <t>33</t>
   </si>
   <si>
-    <t>源类型=type:exeBC; 层级=21</t>
+    <r>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:exeBC; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=21</t>
+    </r>
   </si>
   <si>
     <t>34</t>
@@ -992,7 +1018,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>sntzm_gy(3)</t>
+      <t>sntzm_gy(s1)</t>
     </r>
     <r>
       <rPr>
@@ -1022,7 +1048,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>sntzm_gy(3)</t>
+      <t>sntzm_gy(ns1)</t>
     </r>
     <r>
       <rPr>
@@ -1030,7 +1056,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>, 2)</t>
+      <t>, 1)</t>
     </r>
   </si>
   <si>
@@ -4027,7 +4053,7 @@
       <c r="K33" t="s">
         <v>15</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L33" s="2" t="s">
         <v>113</v>
       </c>
     </row>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20010" windowHeight="11460"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_盖亚之心（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="495">
   <si>
     <t>ID</t>
   </si>
@@ -288,6 +288,9 @@
     <t>也许那就是我们，现实里的我们。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_David; 层级=19</t>
   </si>
   <si>
@@ -376,6 +379,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -497,6 +505,9 @@
     <t>整面照片墙发出一阵沉闷的吱呀声，照片中的盖曼像是被一把无形的利刃从正中央劈开——整面照片墙发出一阵沉闷的吱呀声，照片中的盖曼像是被一把无形的利刃从正中央劈开——</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=31</t>
   </si>
   <si>
@@ -677,7 +688,7 @@
     <t>房间大约四十平米，比你们在楼上见过的所有密室都更规整。墙壁不是水泥或砖石，而是某种泛着哑光的浅灰色板材，拼接处的缝隙被仔细打磨过，仿佛每天都有人定期打扫这里的污渍。</t>
   </si>
   <si>
-    <t>bgfade(sntzm_gy(2)_66,1)</t>
+    <t>bgfade(sntzm_gy(2)_66,1)&amp;unlockscene(scene8)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=4</t>
@@ -856,6 +867,9 @@
     <t>话音刚落，一阵轻微的脚步声便自培养罐后响起。先是一道阴影浮现，继而显现出一名男子的轮廓。</t>
   </si>
   <si>
+    <t>11 enhanced the_mountain-hope-background</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=22</t>
   </si>
   <si>
@@ -934,6 +948,9 @@
     <t>这里是哪里？你一个人在这里做些什么？</t>
   </si>
   <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Clark; 层级=32</t>
   </si>
   <si>
@@ -1010,6 +1027,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadeout(R,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -1040,6 +1062,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>bgfade(sntzm_gy(2)_66,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -3633,7 +3660,7 @@
         <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -3642,12 +3669,12 @@
         <v>39</v>
       </c>
       <c r="L22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="27" spans="1:12">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3665,7 +3692,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3680,12 +3707,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" ht="55.5" spans="1:12">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>46</v>
@@ -3703,7 +3730,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3715,12 +3742,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" ht="58.5" spans="1:12">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3738,7 +3765,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3750,15 +3777,15 @@
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" ht="90" spans="1:12">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
         <v>46</v>
@@ -3776,7 +3803,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3791,12 +3818,12 @@
         <v>39</v>
       </c>
       <c r="L26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" ht="54" spans="1:12">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3814,7 +3841,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3834,7 +3861,7 @@
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -3852,7 +3879,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3867,12 +3894,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" ht="67.5" spans="1:12">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3890,7 +3917,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3910,7 +3937,7 @@
     </row>
     <row r="30" ht="54" spans="1:12">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3928,7 +3955,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3948,7 +3975,7 @@
     </row>
     <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3966,7 +3993,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3981,12 +4008,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" ht="55.5" spans="1:12">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4004,7 +4031,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4016,12 +4043,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4054,12 +4081,12 @@
         <v>15</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" ht="90" spans="1:12">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4077,7 +4104,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4089,15 +4116,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" ht="55.5" spans="1:12">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4115,7 +4142,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4130,12 +4157,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
@@ -4153,7 +4180,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4168,12 +4195,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" ht="55.5" spans="1:12">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4191,7 +4218,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4206,12 +4233,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4229,7 +4256,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4244,12 +4271,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" ht="28.5" spans="1:12">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -4267,7 +4294,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4282,12 +4309,12 @@
         <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4305,7 +4332,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4320,12 +4347,12 @@
         <v>43</v>
       </c>
       <c r="L40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" ht="40.5" spans="1:12">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4343,7 +4370,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4355,15 +4382,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" ht="55.5" spans="1:12">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4381,7 +4408,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4396,12 +4423,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" ht="57" spans="1:12">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4419,13 +4446,13 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="J43" t="s">
         <v>15</v>
@@ -4434,12 +4461,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" ht="67.5" spans="1:12">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4457,7 +4484,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4469,15 +4496,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" ht="27" spans="1:12">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4495,7 +4522,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4510,12 +4537,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4533,7 +4560,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4545,15 +4572,15 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" ht="40.5" spans="1:12">
       <c r="A47" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4571,7 +4598,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4586,12 +4613,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
@@ -4609,7 +4636,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4624,12 +4651,12 @@
         <v>39</v>
       </c>
       <c r="L48" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4647,7 +4674,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4662,12 +4689,12 @@
         <v>43</v>
       </c>
       <c r="L49" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" ht="28.5" spans="1:12">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
         <v>36</v>
@@ -4685,7 +4712,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4700,12 +4727,12 @@
         <v>39</v>
       </c>
       <c r="L50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" ht="54" spans="1:12">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4723,7 +4750,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4738,12 +4765,12 @@
         <v>43</v>
       </c>
       <c r="L51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" ht="42" spans="1:12">
       <c r="A52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4761,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4776,12 +4803,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
         <v>21</v>
@@ -4799,7 +4826,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4814,12 +4841,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" ht="54" spans="1:12">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4837,7 +4864,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4852,12 +4879,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4875,7 +4902,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4890,12 +4917,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4913,7 +4940,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4928,12 +4955,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" ht="54" spans="1:12">
       <c r="A57" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4951,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4963,15 +4990,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L57" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" ht="90" spans="1:12">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4989,7 +5016,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5001,15 +5028,15 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L58" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" ht="54" spans="1:12">
       <c r="A59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5027,7 +5054,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5042,12 +5069,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" ht="28.5" spans="1:12">
       <c r="A60" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5065,7 +5092,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5080,12 +5107,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" ht="55.5" spans="1:12">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5103,7 +5130,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5114,16 +5141,14 @@
       <c r="J61" t="s">
         <v>15</v>
       </c>
-      <c r="K61" t="s">
-        <v>15</v>
-      </c>
+      <c r="K61"/>
       <c r="L61" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="62" ht="54" spans="1:12">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5141,7 +5166,7 @@
         <v>15</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5153,15 +5178,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L62" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" ht="55.5" spans="1:12">
       <c r="A63" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5179,7 +5204,7 @@
         <v>15</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5191,15 +5216,15 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5217,7 +5242,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5237,7 +5262,7 @@
     </row>
     <row r="65" ht="40.5" spans="1:12">
       <c r="A65" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5255,7 +5280,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5270,12 +5295,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" ht="27" spans="1:12">
       <c r="A66" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5293,7 +5318,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5313,7 +5338,7 @@
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5331,7 +5356,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5346,12 +5371,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5384,21 +5409,21 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5407,7 +5432,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5419,15 +5444,15 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L69" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="70" ht="54" spans="1:12">
       <c r="A70" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5436,7 +5461,7 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -5445,7 +5470,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5462,16 +5487,16 @@
     </row>
     <row r="71" ht="30" spans="1:12">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5480,7 +5505,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5495,12 +5520,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5509,7 +5534,7 @@
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5518,7 +5543,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5533,12 +5558,12 @@
         <v>43</v>
       </c>
       <c r="L72" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" ht="28.5" spans="1:12">
       <c r="A73" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B73" t="s">
         <v>46</v>
@@ -5556,7 +5581,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5571,12 +5596,12 @@
         <v>39</v>
       </c>
       <c r="L73" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" ht="40.5" spans="1:12">
       <c r="A74" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5594,7 +5619,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5614,16 +5639,16 @@
     </row>
     <row r="75" ht="30" spans="1:12">
       <c r="A75" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5632,7 +5657,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5647,12 +5672,12 @@
         <v>39</v>
       </c>
       <c r="L75" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5661,7 +5686,7 @@
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -5670,7 +5695,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5690,16 +5715,16 @@
     </row>
     <row r="77" ht="70.5" spans="1:12">
       <c r="A77" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -5708,7 +5733,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5723,12 +5748,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="78" ht="42" spans="1:12">
       <c r="A78" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5737,7 +5762,7 @@
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -5746,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5761,21 +5786,21 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" ht="30" spans="1:12">
       <c r="A79" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B79" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -5784,7 +5809,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5799,12 +5824,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="80" ht="30" spans="1:12">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="80" ht="45" spans="1:12">
       <c r="A80" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5813,7 +5838,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -5822,13 +5847,13 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
       </c>
       <c r="I80" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="J80" t="s">
         <v>15</v>
@@ -5837,12 +5862,12 @@
         <v>43</v>
       </c>
       <c r="L80" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81" ht="40.5" spans="1:12">
       <c r="A81" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5860,7 +5885,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5875,12 +5900,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="82" ht="40.5" spans="1:12">
       <c r="A82" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5898,7 +5923,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5910,15 +5935,15 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L82" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83" ht="27" spans="1:12">
       <c r="A83" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5936,7 +5961,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5951,12 +5976,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5974,7 +5999,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5989,15 +6014,15 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -6012,7 +6037,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6027,12 +6052,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6050,7 +6075,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6065,12 +6090,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6088,7 +6113,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6103,21 +6128,21 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" ht="30" spans="1:12">
       <c r="A88" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B88" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -6126,7 +6151,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6141,12 +6166,12 @@
         <v>39</v>
       </c>
       <c r="L88" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" ht="40.5" spans="1:12">
       <c r="A89" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6155,7 +6180,7 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -6164,7 +6189,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6179,12 +6204,12 @@
         <v>43</v>
       </c>
       <c r="L89" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="90" ht="60" spans="1:12">
       <c r="A90" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B90" t="s">
         <v>36</v>
@@ -6202,13 +6227,13 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
       </c>
       <c r="I90" t="s">
-        <v>15</v>
+        <v>286</v>
       </c>
       <c r="J90" t="s">
         <v>15</v>
@@ -6217,12 +6242,12 @@
         <v>39</v>
       </c>
       <c r="L90" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="91" ht="55.5" spans="1:12">
       <c r="A91" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6240,7 +6265,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6255,21 +6280,21 @@
         <v>43</v>
       </c>
       <c r="L91" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="92" ht="30" spans="1:12">
       <c r="A92" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B92" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -6278,7 +6303,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6290,15 +6315,15 @@
         <v>15</v>
       </c>
       <c r="K92" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L92" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93" ht="30" spans="1:12">
       <c r="A93" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6307,7 +6332,7 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -6316,7 +6341,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6331,21 +6356,21 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" ht="30" spans="1:12">
       <c r="A94" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B94" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
@@ -6354,7 +6379,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6369,12 +6394,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6383,7 +6408,7 @@
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -6392,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6407,12 +6432,12 @@
         <v>43</v>
       </c>
       <c r="L95" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" ht="28.5" spans="1:12">
       <c r="A96" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B96" t="s">
         <v>46</v>
@@ -6430,7 +6455,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6445,15 +6470,15 @@
         <v>39</v>
       </c>
       <c r="L96" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="97" ht="30" spans="1:12">
       <c r="A97" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B97" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -6465,10 +6490,10 @@
         <v>15</v>
       </c>
       <c r="F97" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G97" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6480,15 +6505,15 @@
         <v>15</v>
       </c>
       <c r="K97" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L97" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" ht="30" spans="1:12">
       <c r="A98" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6503,10 +6528,10 @@
         <v>15</v>
       </c>
       <c r="F98" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G98" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6518,15 +6543,15 @@
         <v>15</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="L98" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="99" ht="225" spans="1:12">
       <c r="A99" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B99" t="s">
         <v>21</v>
@@ -6544,7 +6569,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6556,10 +6581,10 @@
         <v>15</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="L99" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -6580,47 +6605,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -6628,7 +6653,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -6636,66 +6661,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B13" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B14" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B15" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -6717,616 +6742,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D5" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F5" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B6" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C6" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D6" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B7" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D7" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F7" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B8" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C8" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D8" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E8" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F8" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B9" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C9" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D9" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E9" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F9" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B10" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C10" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D10" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E10" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F10" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B11" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C11" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E11" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F11" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C12" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D12" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E12" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F12" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B13" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C13" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D13" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E13" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F13" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B14" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C14" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D14" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E14" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F14" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B15" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C15" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D15" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E15" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F15" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B16" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C16" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D16" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E16" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F16" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B17" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C17" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D17" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E17" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F17" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B18" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C18" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D18" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E18" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F18" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B19" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C19" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D19" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E19" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F19" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B20" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C20" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D20" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E20" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F20" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B21" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C21" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D21" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E21" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F21" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B22" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C22" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D22" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E22" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F22" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B23" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C23" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D23" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E23" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F23" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B24" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C24" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D24" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E24" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F24" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B25" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C25" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D25" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E25" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F25" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B26" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C26" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D26" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E26" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F26" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B27" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C27" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D27" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E27" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F27" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B28" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C28" t="s">
+        <v>478</v>
+      </c>
+      <c r="D28" t="s">
         <v>474</v>
       </c>
-      <c r="D28" t="s">
-        <v>470</v>
-      </c>
       <c r="E28" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F28" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B29" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C29" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D29" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E29" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F29" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B30" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C30" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D30" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E30" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F30" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B31" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C31" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D31" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
